--- a/arquivos de documentação/DICIONARIO_DADOS.xlsx
+++ b/arquivos de documentação/DICIONARIO_DADOS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ian_borba\Documents\GitHub\SA_PADARIAALEMAO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SA_PADARIAALEMAO\arquivos de documentação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D27CACA-A1FB-4223-88F8-9253D10AC72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E58CA9-10BD-4712-8389-5563A1C35B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E0E67480-1290-41CE-BEDF-B6CDD9423F14}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="151">
   <si>
     <t>TABELA PRODUTOS</t>
   </si>
@@ -146,9 +146,6 @@
     <t>CPF</t>
   </si>
   <si>
-    <t>Esta_civíl</t>
-  </si>
-  <si>
     <t>UF</t>
   </si>
   <si>
@@ -173,15 +170,9 @@
     <t>Email</t>
   </si>
   <si>
-    <t>nível_de_acesso</t>
-  </si>
-  <si>
     <t>Data_nascimento</t>
   </si>
   <si>
-    <t>Data_admissão</t>
-  </si>
-  <si>
     <t>Cargo</t>
   </si>
   <si>
@@ -420,13 +411,94 @@
   </si>
   <si>
     <t>ESSE CAMPO IRÁ ARMAZENAR A SENHA TEMPORÁRIA QUE SERA GERADA AUTOMATICAMENTE</t>
+  </si>
+  <si>
+    <t>valor_unitario</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR O VALOR UNITÁRIO DE CADA PRODUTO</t>
+  </si>
+  <si>
+    <t>TABELA VENDAS</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR O STATUS DA COMANDA</t>
+  </si>
+  <si>
+    <t>TABELA PAGAMENTOS</t>
+  </si>
+  <si>
+    <t>ID_pagamento</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO GUARDARÁ A CHAVE PRIMARIA DO PAGAMENTO</t>
+  </si>
+  <si>
+    <t>metodo</t>
+  </si>
+  <si>
+    <t>VARCHAR(50)</t>
+  </si>
+  <si>
+    <t>valor_pago</t>
+  </si>
+  <si>
+    <t>troco</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>datatime</t>
+  </si>
+  <si>
+    <t>ID_func_registro</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO GUARDARÁ O MÉTODO DO PAGAMENTO</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR O VALOR PAGO NO PAGAMENTO</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR O TROCO NECESSÁRIO PRA DEVOLVER AO CLIENTE</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR A DATA DO PAGAMENTO</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR A CHAVE ESTRANGEIRA DO FUNCIONÁRIO</t>
+  </si>
+  <si>
+    <t>TABELA PAGAMENTOS_ITENS</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR O VALOR TOTAL DO PAGAMENTO</t>
+  </si>
+  <si>
+    <t>quantidade</t>
+  </si>
+  <si>
+    <t>ESSE CAMPO IRÁ ARMAZENAR A QUANTIDADE DE ITENS NO PAGAMENTO</t>
+  </si>
+  <si>
+    <t>Esta_civil</t>
+  </si>
+  <si>
+    <t>Data_admissa-o</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -443,13 +515,6 @@
     </font>
     <font>
       <sz val="7"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -576,7 +641,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -596,12 +661,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -609,6 +668,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -620,7 +685,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -960,16 +1024,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDC0BD58-DA6D-4D2F-8BDB-C471F8B94AD8}">
-  <dimension ref="A1:O93"/>
+  <dimension ref="A1:P100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
       <c r="E1" s="14" t="s">
         <v>1</v>
       </c>
@@ -985,27 +1049,27 @@
       <c r="O1" s="14"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="10" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="11" t="s">
+      <c r="D2" s="8"/>
+      <c r="E2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1191,107 +1255,130 @@
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
     </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+    </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
+      <c r="C13" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
+      <c r="A14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
+      <c r="E15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="6"/>
+      <c r="E16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
@@ -1306,15 +1393,15 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="2" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -1329,7 +1416,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="2" t="s">
@@ -1337,7 +1424,7 @@
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
@@ -1352,15 +1439,15 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>34</v>
+        <v>149</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="2" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -1378,10 +1465,12 @@
         <v>35</v>
       </c>
       <c r="B21" s="1"/>
-      <c r="C21" s="2"/>
+      <c r="C21" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="D21" s="2"/>
       <c r="E21" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
@@ -1400,11 +1489,11 @@
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -1423,22 +1512,22 @@
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D23" s="2"/>
-      <c r="E23" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
+      <c r="E23" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="6"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -1446,22 +1535,22 @@
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D24" s="2"/>
-      <c r="E24" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="6"/>
+      <c r="E24" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -1469,11 +1558,11 @@
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -1492,11 +1581,11 @@
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="2" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -1515,11 +1604,11 @@
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="2" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
@@ -1538,11 +1627,11 @@
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="2" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
@@ -1557,15 +1646,15 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="2" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -1580,15 +1669,15 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
@@ -1603,15 +1692,15 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>45</v>
+        <v>150</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
@@ -1626,15 +1715,15 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
@@ -1649,15 +1738,15 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>47</v>
+        <v>121</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="2" t="s">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="3" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
@@ -1670,130 +1759,130 @@
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-      <c r="O34" s="3"/>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="11"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="8"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="8"/>
+      <c r="C37" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="8"/>
+      <c r="E37" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="10"/>
-      <c r="E38" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="11"/>
-      <c r="O38" s="11"/>
+      <c r="A38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="2"/>
+      <c r="E38" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D39" s="2"/>
-      <c r="E39" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
-      <c r="O39" s="3"/>
+      <c r="E39" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="6"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B40" s="1"/>
+      <c r="A40" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B40" s="13"/>
       <c r="C40" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D40" s="2"/>
-      <c r="E40" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
-      <c r="O40" s="6"/>
+      <c r="E40" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B41" s="13"/>
+      <c r="A41" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B41" s="1"/>
       <c r="C41" s="2" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
@@ -1808,15 +1897,15 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="2" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
@@ -1835,11 +1924,11 @@
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
@@ -1858,22 +1947,22 @@
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D44" s="2"/>
-      <c r="E44" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3"/>
-      <c r="O44" s="3"/>
+      <c r="E44" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="6"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
@@ -1881,34 +1970,34 @@
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D45" s="2"/>
-      <c r="E45" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="5"/>
-      <c r="K45" s="5"/>
-      <c r="L45" s="5"/>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5"/>
-      <c r="O45" s="6"/>
+      <c r="E45" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="3"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="2" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
@@ -1923,61 +2012,61 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="2" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D47" s="2"/>
-      <c r="E47" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
-      <c r="O47" s="3"/>
+      <c r="E47" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="6"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D48" s="2"/>
-      <c r="E48" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5"/>
-      <c r="L48" s="5"/>
-      <c r="M48" s="5"/>
-      <c r="N48" s="5"/>
-      <c r="O48" s="6"/>
+      <c r="E48" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="3"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="2" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
@@ -1990,218 +2079,218 @@
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B50" s="1"/>
-      <c r="C50" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D50" s="2"/>
-      <c r="E50" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
-      <c r="O50" s="3"/>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B53" s="10"/>
+      <c r="C53" s="10"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
+      <c r="N53" s="11"/>
+      <c r="O53" s="11"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" s="7"/>
+      <c r="C54" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="8"/>
+      <c r="E54" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="9"/>
+      <c r="K54" s="9"/>
+      <c r="L54" s="9"/>
+      <c r="M54" s="9"/>
+      <c r="N54" s="9"/>
+      <c r="O54" s="9"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="1"/>
+      <c r="C55" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D55" s="2"/>
+      <c r="E55" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="8"/>
-      <c r="I54" s="8"/>
-      <c r="J54" s="8"/>
-      <c r="K54" s="8"/>
-      <c r="L54" s="8"/>
-      <c r="M54" s="8"/>
-      <c r="N54" s="8"/>
-      <c r="O54" s="8"/>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B55" s="9"/>
-      <c r="C55" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="10"/>
-      <c r="E55" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="F55" s="11"/>
-      <c r="G55" s="11"/>
-      <c r="H55" s="11"/>
-      <c r="I55" s="11"/>
-      <c r="J55" s="11"/>
-      <c r="K55" s="11"/>
-      <c r="L55" s="11"/>
-      <c r="M55" s="11"/>
-      <c r="N55" s="11"/>
-      <c r="O55" s="11"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>7</v>
+        <v>92</v>
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="2" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D56" s="2"/>
-      <c r="E56" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-      <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
-      <c r="L56" s="3"/>
-      <c r="M56" s="3"/>
-      <c r="N56" s="3"/>
-      <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+      <c r="E56" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B57" s="1"/>
-      <c r="C57" s="2" t="s">
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="5"/>
+      <c r="K56" s="5"/>
+      <c r="L56" s="5"/>
+      <c r="M56" s="5"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="6"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D57" s="2"/>
-      <c r="E57" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="5"/>
-      <c r="K57" s="5"/>
-      <c r="L57" s="5"/>
-      <c r="M57" s="5"/>
-      <c r="N57" s="5"/>
-      <c r="O57" s="6"/>
+      <c r="B60" s="10"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="11"/>
+      <c r="I60" s="11"/>
+      <c r="J60" s="11"/>
+      <c r="K60" s="11"/>
+      <c r="L60" s="11"/>
+      <c r="M60" s="11"/>
+      <c r="N60" s="11"/>
+      <c r="O60" s="11"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
-      <c r="I61" s="8"/>
-      <c r="J61" s="8"/>
-      <c r="K61" s="8"/>
-      <c r="L61" s="8"/>
-      <c r="M61" s="8"/>
-      <c r="N61" s="8"/>
-      <c r="O61" s="8"/>
+      <c r="C61" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="8"/>
+      <c r="E61" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F61" s="9"/>
+      <c r="G61" s="9"/>
+      <c r="H61" s="9"/>
+      <c r="I61" s="9"/>
+      <c r="J61" s="9"/>
+      <c r="K61" s="9"/>
+      <c r="L61" s="9"/>
+      <c r="M61" s="9"/>
+      <c r="N61" s="9"/>
+      <c r="O61" s="9"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B62" s="9"/>
-      <c r="C62" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="10"/>
-      <c r="E62" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="F62" s="11"/>
-      <c r="G62" s="11"/>
-      <c r="H62" s="11"/>
-      <c r="I62" s="11"/>
-      <c r="J62" s="11"/>
-      <c r="K62" s="11"/>
-      <c r="L62" s="11"/>
-      <c r="M62" s="11"/>
-      <c r="N62" s="11"/>
-      <c r="O62" s="11"/>
+      <c r="A62" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B62" s="1"/>
+      <c r="C62" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D62" s="2"/>
+      <c r="E62" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3"/>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3"/>
+      <c r="O62" s="3"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D63" s="2"/>
-      <c r="E63" s="3" t="s">
+      <c r="E63" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
-      <c r="J63" s="3"/>
-      <c r="K63" s="3"/>
-      <c r="L63" s="3"/>
-      <c r="M63" s="3"/>
-      <c r="N63" s="3"/>
-      <c r="O63" s="3"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="6"/>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>102</v>
+        <v>5</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D64" s="2"/>
-      <c r="E64" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
-      <c r="I64" s="5"/>
-      <c r="J64" s="5"/>
-      <c r="K64" s="5"/>
-      <c r="L64" s="5"/>
-      <c r="M64" s="5"/>
-      <c r="N64" s="5"/>
-      <c r="O64" s="6"/>
+      <c r="E64" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3"/>
+      <c r="O64" s="3"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>5</v>
+        <v>102</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
@@ -2216,15 +2305,15 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="2" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
@@ -2239,15 +2328,15 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="3" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
@@ -2260,49 +2349,72 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
     </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B69" s="10"/>
+      <c r="C69" s="10"/>
+      <c r="D69" s="10"/>
+      <c r="E69" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="11"/>
+      <c r="J69" s="11"/>
+      <c r="K69" s="11"/>
+      <c r="L69" s="11"/>
+      <c r="M69" s="11"/>
+      <c r="N69" s="11"/>
+      <c r="O69" s="11"/>
+    </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70" s="7"/>
+      <c r="C70" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="8"/>
+      <c r="E70" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F70" s="9"/>
+      <c r="G70" s="9"/>
+      <c r="H70" s="9"/>
+      <c r="I70" s="9"/>
+      <c r="J70" s="9"/>
+      <c r="K70" s="9"/>
+      <c r="L70" s="9"/>
+      <c r="M70" s="9"/>
+      <c r="N70" s="9"/>
+      <c r="O70" s="9"/>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B71" s="1"/>
+      <c r="C71" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D71" s="2"/>
+      <c r="E71" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B70" s="7"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="8"/>
-      <c r="N70" s="8"/>
-      <c r="O70" s="8"/>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B71" s="9"/>
-      <c r="C71" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D71" s="10"/>
-      <c r="E71" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="F71" s="11"/>
-      <c r="G71" s="11"/>
-      <c r="H71" s="11"/>
-      <c r="I71" s="11"/>
-      <c r="J71" s="11"/>
-      <c r="K71" s="11"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="11"/>
-      <c r="N71" s="11"/>
-      <c r="O71" s="11"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="3"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="3"/>
+      <c r="L71" s="3"/>
+      <c r="M71" s="3"/>
+      <c r="N71" s="3"/>
+      <c r="O71" s="3"/>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
@@ -2310,147 +2422,147 @@
       </c>
       <c r="B72" s="1"/>
       <c r="C72" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D72" s="2"/>
+      <c r="E72" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D72" s="2"/>
-      <c r="E72" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
-      <c r="J72" s="3"/>
-      <c r="K72" s="3"/>
-      <c r="L72" s="3"/>
-      <c r="M72" s="3"/>
-      <c r="N72" s="3"/>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B73" s="1"/>
-      <c r="C73" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D73" s="2"/>
-      <c r="E73" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F73" s="5"/>
-      <c r="G73" s="5"/>
-      <c r="H73" s="5"/>
-      <c r="I73" s="5"/>
-      <c r="J73" s="5"/>
-      <c r="K73" s="5"/>
-      <c r="L73" s="5"/>
-      <c r="M73" s="5"/>
-      <c r="N73" s="5"/>
-      <c r="O73" s="6"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="5"/>
+      <c r="M72" s="5"/>
+      <c r="N72" s="5"/>
+      <c r="O72" s="6"/>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A76" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B76" s="10"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="10"/>
+      <c r="E76" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="11"/>
+      <c r="J76" s="11"/>
+      <c r="K76" s="11"/>
+      <c r="L76" s="11"/>
+      <c r="M76" s="11"/>
+      <c r="N76" s="11"/>
+      <c r="O76" s="11"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B77" s="7"/>
+      <c r="C77" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="8"/>
+      <c r="E77" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F77" s="9"/>
+      <c r="G77" s="9"/>
+      <c r="H77" s="9"/>
+      <c r="I77" s="9"/>
+      <c r="J77" s="9"/>
+      <c r="K77" s="9"/>
+      <c r="L77" s="9"/>
+      <c r="M77" s="9"/>
+      <c r="N77" s="9"/>
+      <c r="O77" s="9"/>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8"/>
-      <c r="J77" s="8"/>
-      <c r="K77" s="8"/>
-      <c r="L77" s="8"/>
-      <c r="M77" s="8"/>
-      <c r="N77" s="8"/>
-      <c r="O77" s="8"/>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A78" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B78" s="9"/>
-      <c r="C78" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="10"/>
-      <c r="E78" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="F78" s="11"/>
-      <c r="G78" s="11"/>
-      <c r="H78" s="11"/>
-      <c r="I78" s="11"/>
-      <c r="J78" s="11"/>
-      <c r="K78" s="11"/>
-      <c r="L78" s="11"/>
-      <c r="M78" s="11"/>
-      <c r="N78" s="11"/>
-      <c r="O78" s="11"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D78" s="2"/>
+      <c r="E78" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3"/>
+      <c r="L78" s="3"/>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3"/>
+      <c r="O78" s="3"/>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c r="B79" s="1"/>
       <c r="C79" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D79" s="2"/>
-      <c r="E79" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
-      <c r="J79" s="3"/>
-      <c r="K79" s="3"/>
-      <c r="L79" s="3"/>
-      <c r="M79" s="3"/>
-      <c r="N79" s="3"/>
-      <c r="O79" s="3"/>
+      <c r="E79" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F79" s="5"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="5"/>
+      <c r="K79" s="5"/>
+      <c r="L79" s="5"/>
+      <c r="M79" s="5"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="6"/>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>27</v>
+        <v>116</v>
       </c>
       <c r="B80" s="1"/>
       <c r="C80" s="2" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="D80" s="2"/>
-      <c r="E80" s="4" t="s">
+      <c r="E80" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F80" s="5"/>
-      <c r="G80" s="5"/>
-      <c r="H80" s="5"/>
-      <c r="I80" s="5"/>
-      <c r="J80" s="5"/>
-      <c r="K80" s="5"/>
-      <c r="L80" s="5"/>
-      <c r="M80" s="5"/>
-      <c r="N80" s="5"/>
-      <c r="O80" s="6"/>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3"/>
+      <c r="K80" s="3"/>
+      <c r="L80" s="3"/>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3"/>
+      <c r="O80" s="3"/>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>119</v>
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="2" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
@@ -2463,17 +2575,17 @@
       <c r="N81" s="3"/>
       <c r="O81" s="3"/>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="2" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
@@ -2485,119 +2597,503 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C92" s="15"/>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C93" s="15"/>
+      <c r="P82" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A84" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B84" s="10"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="10"/>
+      <c r="E84" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F84" s="11"/>
+      <c r="G84" s="11"/>
+      <c r="H84" s="11"/>
+      <c r="I84" s="11"/>
+      <c r="J84" s="11"/>
+      <c r="K84" s="11"/>
+      <c r="L84" s="11"/>
+      <c r="M84" s="11"/>
+      <c r="N84" s="11"/>
+      <c r="O84" s="11"/>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A85" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B85" s="7"/>
+      <c r="C85" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="8"/>
+      <c r="E85" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F85" s="9"/>
+      <c r="G85" s="9"/>
+      <c r="H85" s="9"/>
+      <c r="I85" s="9"/>
+      <c r="J85" s="9"/>
+      <c r="K85" s="9"/>
+      <c r="L85" s="9"/>
+      <c r="M85" s="9"/>
+      <c r="N85" s="9"/>
+      <c r="O85" s="9"/>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B86" s="1"/>
+      <c r="C86" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D86" s="2"/>
+      <c r="E86" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="3"/>
+      <c r="J86" s="3"/>
+      <c r="K86" s="3"/>
+      <c r="L86" s="3"/>
+      <c r="M86" s="3"/>
+      <c r="N86" s="3"/>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B87" s="1"/>
+      <c r="C87" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D87" s="2"/>
+      <c r="E87" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3"/>
+      <c r="K87" s="3"/>
+      <c r="L87" s="3"/>
+      <c r="M87" s="3"/>
+      <c r="N87" s="3"/>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B88" s="1"/>
+      <c r="C88" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D88" s="2"/>
+      <c r="E88" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="3"/>
+      <c r="J88" s="3"/>
+      <c r="K88" s="3"/>
+      <c r="L88" s="3"/>
+      <c r="M88" s="3"/>
+      <c r="N88" s="3"/>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B89" s="1"/>
+      <c r="C89" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D89" s="2"/>
+      <c r="E89" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
+      <c r="I89" s="3"/>
+      <c r="J89" s="3"/>
+      <c r="K89" s="3"/>
+      <c r="L89" s="3"/>
+      <c r="M89" s="3"/>
+      <c r="N89" s="3"/>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B90" s="1"/>
+      <c r="C90" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D90" s="2"/>
+      <c r="E90" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+      <c r="I90" s="3"/>
+      <c r="J90" s="3"/>
+      <c r="K90" s="3"/>
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B91" s="1"/>
+      <c r="C91" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D91" s="2"/>
+      <c r="E91" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+      <c r="I91" s="3"/>
+      <c r="J91" s="3"/>
+      <c r="K91" s="3"/>
+      <c r="L91" s="3"/>
+      <c r="M91" s="3"/>
+      <c r="N91" s="3"/>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B92" s="1"/>
+      <c r="C92" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D92" s="2"/>
+      <c r="E92" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="3"/>
+      <c r="K92" s="3"/>
+      <c r="L92" s="3"/>
+      <c r="M92" s="3"/>
+      <c r="N92" s="3"/>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A94" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B94" s="10"/>
+      <c r="C94" s="10"/>
+      <c r="D94" s="10"/>
+      <c r="E94" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F94" s="11"/>
+      <c r="G94" s="11"/>
+      <c r="H94" s="11"/>
+      <c r="I94" s="11"/>
+      <c r="J94" s="11"/>
+      <c r="K94" s="11"/>
+      <c r="L94" s="11"/>
+      <c r="M94" s="11"/>
+      <c r="N94" s="11"/>
+      <c r="O94" s="11"/>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A95" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B95" s="7"/>
+      <c r="C95" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="8"/>
+      <c r="E95" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F95" s="9"/>
+      <c r="G95" s="9"/>
+      <c r="H95" s="9"/>
+      <c r="I95" s="9"/>
+      <c r="J95" s="9"/>
+      <c r="K95" s="9"/>
+      <c r="L95" s="9"/>
+      <c r="M95" s="9"/>
+      <c r="N95" s="9"/>
+      <c r="O95" s="9"/>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B96" s="1"/>
+      <c r="C96" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D96" s="2"/>
+      <c r="E96" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="3"/>
+      <c r="J96" s="3"/>
+      <c r="K96" s="3"/>
+      <c r="L96" s="3"/>
+      <c r="M96" s="3"/>
+      <c r="N96" s="3"/>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B97" s="1"/>
+      <c r="C97" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D97" s="2"/>
+      <c r="E97" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+      <c r="I97" s="3"/>
+      <c r="J97" s="3"/>
+      <c r="K97" s="3"/>
+      <c r="L97" s="3"/>
+      <c r="M97" s="3"/>
+      <c r="N97" s="3"/>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B98" s="1"/>
+      <c r="C98" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D98" s="2"/>
+      <c r="E98" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="3"/>
+      <c r="J98" s="3"/>
+      <c r="K98" s="3"/>
+      <c r="L98" s="3"/>
+      <c r="M98" s="3"/>
+      <c r="N98" s="3"/>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B99" s="1"/>
+      <c r="C99" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D99" s="2"/>
+      <c r="E99" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+      <c r="I99" s="3"/>
+      <c r="J99" s="3"/>
+      <c r="K99" s="3"/>
+      <c r="L99" s="3"/>
+      <c r="M99" s="3"/>
+      <c r="N99" s="3"/>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B100" s="1"/>
+      <c r="C100" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D100" s="2"/>
+      <c r="E100" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="3"/>
+      <c r="J100" s="3"/>
+      <c r="K100" s="3"/>
+      <c r="L100" s="3"/>
+      <c r="M100" s="3"/>
+      <c r="N100" s="3"/>
+      <c r="O100" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="194">
+  <mergeCells count="246">
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="E98:O98"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="E99:O99"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="E100:O100"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="E94:O94"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="E95:O95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="E96:O96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="E97:O97"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="E90:O90"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="E91:O91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="E92:O92"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="E87:O87"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="E88:O88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="E89:O89"/>
     <mergeCell ref="A82:B82"/>
     <mergeCell ref="C82:D82"/>
     <mergeCell ref="E82:O82"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="E34:O34"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="E80:O80"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="E81:O81"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="E78:O78"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="E79:O79"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="E73:O73"/>
-    <mergeCell ref="A77:D77"/>
-    <mergeCell ref="E77:O77"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="E71:O71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="E72:O72"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="E67:O67"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="E70:O70"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:O65"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="E66:O66"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:O63"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="E64:O64"/>
-    <mergeCell ref="A61:D61"/>
-    <mergeCell ref="E61:O61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="E62:O62"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:O57"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="E55:O55"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="E56:O56"/>
-    <mergeCell ref="E54:O54"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E49:O49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="E50:O50"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="E47:O47"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="E48:O48"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="E45:O45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="E46:O46"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="E43:O43"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="E44:O44"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="E41:O41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="E42:O42"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="E39:O39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="E40:O40"/>
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="E84:O84"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="E85:O85"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="E86:O86"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:O32"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:O29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:O30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:O31"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:O22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:O23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:O24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:O25"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:O26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:O27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:O28"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:O19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:O20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:O21"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:O16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:O17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:O18"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:O10"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="E12:O12"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:O14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:O15"/>
+    <mergeCell ref="E6:O6"/>
+    <mergeCell ref="E7:O7"/>
+    <mergeCell ref="E4:O4"/>
+    <mergeCell ref="E8:O8"/>
+    <mergeCell ref="E9:O9"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="E1:O1"/>
-    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="E36:O36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:D37"/>
     <mergeCell ref="E37:O37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="E38:O38"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
@@ -2610,84 +3106,113 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:O14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:O13"/>
     <mergeCell ref="E2:O2"/>
     <mergeCell ref="E3:O3"/>
     <mergeCell ref="E5:O5"/>
-    <mergeCell ref="E6:O6"/>
-    <mergeCell ref="E7:O7"/>
-    <mergeCell ref="E4:O4"/>
-    <mergeCell ref="E8:O8"/>
-    <mergeCell ref="E9:O9"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:O10"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="E13:O13"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:O15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:O16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:O17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:O18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:O19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:O20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:O21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:O22"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:O23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:O24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:O25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:O26"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:O27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:O28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:O29"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="E40:O40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="E41:O41"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="E38:O38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E39:O39"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="E44:O44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="E45:O45"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="E42:O42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="E43:O43"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="E48:O48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:O49"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E46:O46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="E47:O47"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="E60:O60"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="E61:O61"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="E56:O56"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="E54:O54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="E55:O55"/>
+    <mergeCell ref="E53:O53"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:O64"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:O65"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:O62"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:O63"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="E70:O70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="E71:O71"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="E66:O66"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="E69:O69"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="E67:O67"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="E81:O81"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="E33:O33"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:O30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:O31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:O32"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="E79:O79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="E80:O80"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="E77:O77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="E78:O78"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="E72:O72"/>
+    <mergeCell ref="A76:D76"/>
+    <mergeCell ref="E76:O76"/>
+    <mergeCell ref="A70:B70"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
